--- a/ihale-analiz/templates/excel/birim-fiyat.xlsx
+++ b/ihale-analiz/templates/excel/birim-fiyat.xlsx
@@ -19,7 +19,6 @@
   </sheets>
   <definedNames>
     <definedName name="MetrajTol">'Özet'!$B$17</definedName>
-    <definedName name="PursantajTol">'Özet'!$B$18</definedName>
     <definedName name="YaklasikMaliyet">'Özet'!$B$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BFTC Kıyas'!$A$4:$N$504</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'BFTC Kıyas'!$4:$4</definedName>
@@ -589,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -853,20 +852,10 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Pursantaj Toleransı (puan)</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
           <t>Analiz Tarihi</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n"/>
+      <c r="B18" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/ihale-analiz/templates/excel/birim-fiyat.xlsx
+++ b/ihale-analiz/templates/excel/birim-fiyat.xlsx
@@ -633,7 +633,7 @@
       <c r="B4" s="5" t="n"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Teklif tutarı (idare miktarı)</t>
+          <t>İdare Yaklaşık Maliyet</t>
         </is>
       </c>
       <c r="E4" s="6">
@@ -667,7 +667,7 @@
       <c r="B6" s="5" t="n"/>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Teklif / yaklaşık maliyet</t>
+          <t>İdare YM / açıklanan yaklaşık maliyet</t>
         </is>
       </c>
       <c r="E6" s="7">
